--- a/tame_output/ON/bt/strategyON_20231029.xlsx
+++ b/tame_output/ON/bt/strategyON_20231029.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.4%</t>
+          <t>132.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.4%</t>
+          <t>126.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1764"/>
+  <dimension ref="A1:G1765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42082,7 +42082,7 @@
         <v>45226</v>
       </c>
       <c r="B1764" t="n">
-        <v>3.048350097323861</v>
+        <v>3.049222094320088</v>
       </c>
       <c r="C1764" t="n">
         <v>3.030639375029551</v>
@@ -42098,6 +42098,29 @@
       </c>
       <c r="G1764" t="n">
         <v>4.327166856593275</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="2" t="n">
+        <v>45227</v>
+      </c>
+      <c r="B1765" t="n">
+        <v>3.047430549460563</v>
+      </c>
+      <c r="C1765" t="n">
+        <v>3.030564355893199</v>
+      </c>
+      <c r="D1765" t="n">
+        <v>1.534125367633645</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>3.64385807863291</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>2.163255588220161</v>
+      </c>
+      <c r="G1765" t="n">
+        <v>4.328517708825297</v>
       </c>
     </row>
   </sheetData>
